--- a/results/Int All Data 0.7/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.7/Linea_fi_explain.xlsx
@@ -1829,7 +1829,7 @@
         <v>0.000162685325616504</v>
       </c>
       <c r="BA3" t="n">
-        <v>-3.403728552858329e-05</v>
+        <v>-3.931433038346444e-05</v>
       </c>
       <c r="BB3" t="n">
         <v>0.0007547255506757211</v>
@@ -1892,7 +1892,7 @@
         <v>0.007170340896471639</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01685828011443609</v>
+        <v>0.01685871325851608</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0001870370626905671</v>
@@ -1922,7 +1922,7 @@
         <v>0.003783654481767903</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0001364123885243728</v>
+        <v>0.0001413239798799714</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4674889861071022</v>
@@ -1958,7 +1958,7 @@
         <v>0.04368362349159009</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.03535887316102976</v>
+        <v>0.03536421789646536</v>
       </c>
       <c r="CS3" t="n">
         <v>0.3167783107808362</v>
@@ -1979,7 +1979,7 @@
         <v>0.01343121938073257</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.01811764301523501</v>
+        <v>0.01811241015285929</v>
       </c>
       <c r="CZ3" t="n">
         <v>0.0004066715779723584</v>
@@ -2030,7 +2030,7 @@
         <v>0.01442216343560214</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01669323042855708</v>
+        <v>0.01668294498165903</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0.0001086551165345784</v>
@@ -2042,7 +2042,7 @@
         <v>0.001041916022044972</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.01559305643517256</v>
+        <v>0.01560909064147935</v>
       </c>
       <c r="DU3" t="n">
         <v>0.02043370055068428</v>
@@ -2054,7 +2054,7 @@
         <v>0.0006891635794834149</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.005321214452126842</v>
+        <v>0.005327238548512385</v>
       </c>
       <c r="DY3" t="n">
         <v>0.04816283494813915</v>
@@ -2111,7 +2111,7 @@
         <v>-0.0001205312205390741</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.002058258766621784</v>
+        <v>0.002042802816080823</v>
       </c>
       <c r="ER3" t="n">
         <v>-0.0006913954322057836</v>
@@ -2298,7 +2298,7 @@
         <v>0.00301575301344649</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007869865322791878</v>
+        <v>0.007874574193568365</v>
       </c>
       <c r="BB4" t="n">
         <v>0.003894592343023526</v>
@@ -2361,7 +2361,7 @@
         <v>0.0136485880662662</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01978343649707207</v>
+        <v>0.01978436316152922</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0004929802431850802</v>
@@ -2391,7 +2391,7 @@
         <v>0.006959896795337987</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002946043900503337</v>
+        <v>0.002943465449594103</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1015828711685263</v>
@@ -2427,7 +2427,7 @@
         <v>0.03670874471674392</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.03948778417542372</v>
+        <v>0.03950171062588283</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1083396134520513</v>
@@ -2448,7 +2448,7 @@
         <v>0.02446824377511617</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02485781877968588</v>
+        <v>0.02486155992714737</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.0013246115617667</v>
@@ -2499,7 +2499,7 @@
         <v>0.02624463012600208</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.03611029808994178</v>
+        <v>0.03610061165344598</v>
       </c>
       <c r="DQ4" t="n">
         <v>0.0004912935033476438</v>
@@ -2511,7 +2511,7 @@
         <v>0.001738239849258726</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.03107638743517282</v>
+        <v>0.0310976940181237</v>
       </c>
       <c r="DU4" t="n">
         <v>0.03819208921257773</v>
@@ -2523,7 +2523,7 @@
         <v>0.002538777055613641</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01267785147037315</v>
+        <v>0.01268837830907377</v>
       </c>
       <c r="DY4" t="n">
         <v>0.04902916052870145</v>
@@ -2580,7 +2580,7 @@
         <v>0.0003683395120135994</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.005656593238342003</v>
+        <v>0.005654919497633099</v>
       </c>
       <c r="ER4" t="n">
         <v>0.001597751856221613</v>
@@ -3299,7 +3299,7 @@
         <v>-0.000481026189203601</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001534097889512057</v>
+        <v>0.001510622792934049</v>
       </c>
       <c r="BW6" t="n">
         <v>-3.957783641160839e-05</v>
@@ -3329,7 +3329,7 @@
         <v>0.0003874933190807284</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0009878807962695134</v>
+        <v>-0.0009510438611025241</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3810248821767316</v>
@@ -3386,7 +3386,7 @@
         <v>-0.0003430284632199049</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.003156921653723399</v>
+        <v>0.003117675185905505</v>
       </c>
       <c r="CZ6" t="n">
         <v>-0.0003293472161802369</v>
@@ -4375,7 +4375,7 @@
         <v>0.01364154670287968</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001997693459569161</v>
+        <v>0.001985341680913033</v>
       </c>
       <c r="DQ8" t="n">
         <v>0.0001605403528052107</v>
@@ -4456,7 +4456,7 @@
         <v>8.0171031533946e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.002476937920939254</v>
+        <v>0.002361018291882053</v>
       </c>
       <c r="ER8" t="n">
         <v>3.92464678179022e-05</v>
@@ -4772,7 +4772,7 @@
         <v>0.1105180533751963</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1279529663281668</v>
+        <v>0.1280064136825228</v>
       </c>
       <c r="CS9" t="n">
         <v>0.4519268774703559</v>
@@ -4844,7 +4844,7 @@
         <v>0.0834847675040086</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.09000534473543562</v>
+        <v>0.08995189738107966</v>
       </c>
       <c r="DQ9" t="n">
         <v>0.0004636785162287382</v>
